--- a/app/data/walkthrough/Danube One App Walkthrough(1).xlsx
+++ b/app/data/walkthrough/Danube One App Walkthrough(1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandini.agrawal_info\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Danube Properties\Chatbot Initiative Github\Danube-One-Chatbot-Production\app\data\walkthrough\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87C6E3F-D97F-42EA-A04D-E2283D6313BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC14B1A-70AA-4B32-B57D-7839F13E1D3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,12 +128,6 @@
     <t>Change Password</t>
   </si>
   <si>
-    <t>Step 1: Select or search project from the UNITS tab on the navigation bar.
-Step 2: Scroll to the Settings section -&gt; Select Change Password.
-Step 3: Enter the current password and the new password.
-Step 4: Select Submit to update the password and login back with the new password.</t>
-  </si>
-  <si>
     <t>ChangePassword</t>
   </si>
   <si>
@@ -330,6 +324,12 @@
   </si>
   <si>
     <t>DAR Dashboard</t>
+  </si>
+  <si>
+    <t>Step 1: Select the MENU tab from the navigation bar.
+Step 2: Scroll to the Settings section -&gt; Select Change Password.
+Step 3: Enter the current password and the new password.
+Step 4: Click on Change Password to update the password and login back with the new password.</t>
   </si>
 </sst>
 </file>
@@ -968,7 +968,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="37.5">
@@ -996,7 +996,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="71.25" customHeight="1">
@@ -1049,10 +1049,10 @@
         <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="61.5" customHeight="1">
@@ -1060,13 +1060,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="81.75" customHeight="1">
@@ -1074,13 +1074,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="96" customHeight="1">
@@ -1088,13 +1088,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="76.5" customHeight="1">
@@ -1102,13 +1102,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="84.75" customHeight="1">
@@ -1116,13 +1116,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" customHeight="1">
@@ -1130,13 +1130,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="16" t="s">
         <v>45</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="111.75" customHeight="1">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="B17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="D17" s="19" t="s">
         <v>48</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="48.75" customHeight="1">
@@ -1158,13 +1158,13 @@
         <v>18</v>
       </c>
       <c r="B18" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>51</v>
-      </c>
       <c r="D18" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.5" customHeight="1">
@@ -1172,13 +1172,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="D19" s="22" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="43.5">
@@ -1186,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="31" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>56</v>
       </c>
       <c r="D20" s="18"/>
     </row>
@@ -1198,13 +1198,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="43.5">
@@ -1212,10 +1212,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="31" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>60</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>6</v>
@@ -1226,13 +1226,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="D23" s="18" t="s">
         <v>62</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
@@ -1248,10 +1248,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>64</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>65</v>
       </c>
       <c r="D25" s="30"/>
     </row>
